--- a/publication_tables/main/table5.xlsx
+++ b/publication_tables/main/table5.xlsx
@@ -460,7 +460,7 @@
         <v>3.62</v>
       </c>
       <c r="D2" t="n">
-        <v>6.675</v>
+        <v>6.681</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -480,13 +480,13 @@
         <v>6.33</v>
       </c>
       <c r="D3" t="n">
-        <v>6.775</v>
+        <v>6.781</v>
       </c>
       <c r="E3" t="n">
-        <v>92.84999999999999</v>
+        <v>92.84</v>
       </c>
       <c r="F3" t="n">
-        <v>17.87</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="4">
@@ -500,7 +500,7 @@
         <v>15.71</v>
       </c>
       <c r="D4" t="n">
-        <v>7.024</v>
+        <v>7.031</v>
       </c>
       <c r="E4" t="n">
         <v>75</v>
@@ -517,16 +517,16 @@
         <v>27.05</v>
       </c>
       <c r="C5" t="n">
-        <v>22.75</v>
+        <v>22.76</v>
       </c>
       <c r="D5" t="n">
-        <v>7.175</v>
+        <v>7.181</v>
       </c>
       <c r="E5" t="n">
-        <v>64.23</v>
+        <v>64.22</v>
       </c>
       <c r="F5" t="n">
-        <v>55.23</v>
+        <v>55.24</v>
       </c>
     </row>
     <row r="6">
@@ -534,13 +534,13 @@
         <v>0.699</v>
       </c>
       <c r="B6" t="n">
-        <v>43.17</v>
+        <v>43.16</v>
       </c>
       <c r="C6" t="n">
-        <v>36.32</v>
+        <v>36.31</v>
       </c>
       <c r="D6" t="n">
-        <v>7.374</v>
+        <v>7.38</v>
       </c>
       <c r="E6" t="n">
         <v>50</v>
@@ -560,10 +560,10 @@
         <v>84.13</v>
       </c>
       <c r="D7" t="n">
-        <v>7.725</v>
+        <v>7.732</v>
       </c>
       <c r="E7" t="n">
-        <v>24.86</v>
+        <v>24.84</v>
       </c>
       <c r="F7" t="n">
         <v>100</v>
@@ -580,114 +580,90 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Table</t>
+          <t>Variable</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Table 5. Selected PMT designs under poverty-performance constraints</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Note</t>
+          <t>Tolerance (pp)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Note. Tolerance is the increase from minimum FGT1; the retained gain is the share of the maximum FGT1 reduction relative to the unsupported shock. The target population comprises the two lowest benchmark income groups. Net cost is 0.5% of GDP in every row. pp: percentage points. Source: model simulations.</t>
+          <t>Permitted increase above minimum FGT1, percentage points. Values follow the displayed precision of Table 5. Selected PMT designs under poverty-performance constraints. Full-precision simulation results accompany the analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Coverage (%)</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Population share receiving cash, percent. Values follow the displayed precision of Table 5. Selected PMT designs under poverty-performance constraints. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Variable</t>
+          <t>Recipients (million)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Represented cash recipients, millions. Values follow the displayed precision of Table 5. Selected PMT designs under poverty-performance constraints. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Tolerance (pp)</t>
+          <t>FGT1 (%)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Permitted FGT1 increase from the numerical minimum (percentage points).</t>
+          <t>FGT1 poverty-gap index, percent. Values follow the displayed precision of Table 5. Selected PMT designs under poverty-performance constraints. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coverage (%)</t>
+          <t>Gain retained (%)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Share of represented persons receiving cash (%).</t>
+          <t>Share of the maximum reduction from the unsupported shock retained, percent. Values follow the displayed precision of Table 5. Selected PMT designs under poverty-performance constraints. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Recipients (million)</t>
+          <t>Target population reached (%)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Represented number of cash recipients (million persons).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>FGT1 (%)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Poverty-gap index at the selected coverage (%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Gain retained (%)</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Share of the maximum attainable FGT1 reduction from the unsupported shock retained (%).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Target population reached (%)</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Share of the fixed bottom-two-quintile target population receiving cash (%).</t>
+          <t>Share of the initial bottom-two-quintile target population receiving cash, percent. Values follow the displayed precision of Table 5. Selected PMT designs under poverty-performance constraints. Full-precision simulation results accompany the analysis.</t>
         </is>
       </c>
     </row>
